--- a/data/trans_dic/IP12B$herida-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$herida-Estudios-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por síntomas o dolor por contusión, lesión o heridas</t>
+          <t>Menores que han limitado su actividad por síntomas o dolor por contusión, lesión o heridas (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,27 +678,27 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 20,75</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 11,83</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 49,21</t>
+          <t>0,0; 56,72</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 66,41</t>
+          <t>0,0; 66,84</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 45,64</t>
+          <t>0,0; 51,21</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -707,17 +708,17 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,07</t>
+          <t>0,0; 39,83</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,13</t>
+          <t>0,0; 21,2</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6,36; 51,7</t>
+          <t>6,09; 51,72</t>
         </is>
       </c>
     </row>
@@ -787,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,6</t>
+          <t>0,0; 14,79</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,08</t>
+          <t>0,0; 11,76</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,15</t>
+          <t>0,0; 19,95</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,52</t>
+          <t>0,0; 8,8</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,95</t>
+          <t>0,0; 9,23</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,6; 14,19</t>
+          <t>1,64; 13,14</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,47</t>
+          <t>0,0; 8,44</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,74; 6,45</t>
+          <t>0,75; 6,61</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,68; 11,1</t>
+          <t>1,9; 11,68</t>
         </is>
       </c>
     </row>
@@ -897,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,74</t>
+          <t>0,0; 36,38</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,66</t>
+          <t>0,0; 20,06</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,17</t>
+          <t>0,0; 19,37</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 11,83</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 49,23</t>
+          <t>0,0; 49,59</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 41,86</t>
+          <t>0,0; 41,46</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,58</t>
+          <t>0,0; 15,09</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,43; 23,09</t>
+          <t>2,43; 22,29</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,08; 16,98</t>
+          <t>2,14; 17,0</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,1</t>
+          <t>0,0; 9,64</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,51</t>
+          <t>0,0; 6,55</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,05; 13,28</t>
+          <t>2,09; 13,77</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,44; 12,2</t>
+          <t>1,47; 12,46</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,18; 14,3</t>
+          <t>2,36; 13,91</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,7; 15,71</t>
+          <t>2,75; 16,18</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,52; 8,81</t>
+          <t>1,57; 8,81</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,94; 8,49</t>
+          <t>1,81; 8,59</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,68; 12,0</t>
+          <t>3,57; 11,51</t>
         </is>
       </c>
     </row>
@@ -1071,4 +1072,791 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que han limitado su actividad por síntomas o dolor por contusión, lesión o heridas (tasa de respuesta: 99,36%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1228</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>1502</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>787</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>662</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>1502</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>787</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>1890</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3732</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3679</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3609</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2239</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4444</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3627</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>537; 4561</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>777</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>697</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1554</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>685</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>1223</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>1921</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>1462</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>1920</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>3476</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4381</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4121</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>0; 6348</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0; 2758</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4179</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>597; 4777</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>0; 5144</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>603; 5310</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>1293; 7965</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>613</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>656</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>605</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>1865</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>1175</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>613</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>2521</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>1780</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3128</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3246</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3239</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0; 5563</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3834</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2784</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>666; 6108</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>555; 4416</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>1389</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>1353</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>3388</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>2187</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>3875</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>3759</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>3576</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>5228</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>7146</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4230</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4015</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>1151; 7592</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>685; 5818</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>1499; 8841</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>1318; 7746</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>1426; 7980</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>2255; 10719</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>3680; 11856</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP12B$herida-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$herida-Estudios-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por síntomas o dolor por contusión, lesión o heridas (tasa de respuesta: 99,36%)</t>
+          <t>Menores que en las últimas 2 semanas han limitado su actividad por síntomas o dolor por contusión, lesión o heridas (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -688,17 +688,17 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 56,72</t>
+          <t>0,0; 56,88</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 66,84</t>
+          <t>0,0; 66,6</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 51,21</t>
+          <t>0,0; 43,86</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -708,17 +708,17 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,83</t>
+          <t>0,0; 45,0</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,2</t>
+          <t>0,0; 23,24</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6,09; 51,72</t>
+          <t>6,07; 49,67</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,79</t>
+          <t>0,0; 13,04</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,76</t>
+          <t>0,0; 10,05</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,95</t>
+          <t>0,0; 19,28</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,8</t>
+          <t>0,0; 11,09</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,23</t>
+          <t>0,0; 8,56</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,64; 13,14</t>
+          <t>1,57; 14,2</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,44</t>
+          <t>0,0; 8,33</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,75; 6,61</t>
+          <t>0,75; 6,23</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,9; 11,68</t>
+          <t>1,69; 11,81</t>
         </is>
       </c>
     </row>
@@ -898,17 +898,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,38</t>
+          <t>0,0; 32,55</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,06</t>
+          <t>0,0; 19,55</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,37</t>
+          <t>0,0; 17,69</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -918,27 +918,27 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 49,59</t>
+          <t>0,0; 44,14</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 41,46</t>
+          <t>0,0; 38,21</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,09</t>
+          <t>0,0; 14,89</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,43; 22,29</t>
+          <t>2,43; 24,48</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,14; 17,0</t>
+          <t>2,04; 18,07</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,64</t>
+          <t>0,0; 9,69</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,55</t>
+          <t>0,0; 6,75</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,09; 13,77</t>
+          <t>2,18; 13,53</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,47; 12,46</t>
+          <t>1,47; 11,77</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,36; 13,91</t>
+          <t>1,96; 13,73</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,75; 16,18</t>
+          <t>2,68; 14,96</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,57; 8,81</t>
+          <t>1,44; 8,58</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,81; 8,59</t>
+          <t>1,75; 7,98</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,57; 11,51</t>
+          <t>3,59; 11,61</t>
         </is>
       </c>
     </row>
@@ -1099,7 +1099,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por síntomas o dolor por contusión, lesión o heridas (tasa de respuesta: 99,36%)</t>
+          <t>Menores que en las últimas 2 semanas han limitado su actividad por síntomas o dolor por contusión, lesión o heridas (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1316,17 +1316,17 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 3732</t>
+          <t>0; 3743</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 3679</t>
+          <t>0; 3665</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 3609</t>
+          <t>0; 3091</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1336,17 +1336,17 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 4444</t>
+          <t>0; 5020</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 3627</t>
+          <t>0; 3977</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>537; 4561</t>
+          <t>535; 4381</t>
         </is>
       </c>
     </row>
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 4381</t>
+          <t>0; 3863</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 4121</t>
+          <t>0; 3521</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 6348</t>
+          <t>0; 6135</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 2758</t>
+          <t>0; 3475</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 4179</t>
+          <t>0; 3878</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>597; 4777</t>
+          <t>570; 5166</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 5144</t>
+          <t>0; 5079</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>603; 5310</t>
+          <t>602; 5001</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1293; 7965</t>
+          <t>1152; 8056</t>
         </is>
       </c>
     </row>
@@ -1632,17 +1632,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 3128</t>
+          <t>0; 2799</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 3246</t>
+          <t>0; 3163</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 3239</t>
+          <t>0; 2959</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1652,27 +1652,27 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 5563</t>
+          <t>0; 4951</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 3834</t>
+          <t>0; 3533</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 2784</t>
+          <t>0; 2747</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>666; 6108</t>
+          <t>666; 6707</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>555; 4416</t>
+          <t>531; 4694</t>
         </is>
       </c>
     </row>
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 4230</t>
+          <t>0; 4251</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 4015</t>
+          <t>0; 4139</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1151; 7592</t>
+          <t>1200; 7458</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>685; 5818</t>
+          <t>686; 5499</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1499; 8841</t>
+          <t>1248; 8726</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1318; 7746</t>
+          <t>1284; 7162</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1426; 7980</t>
+          <t>1306; 7770</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2255; 10719</t>
+          <t>2181; 9965</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3680; 11856</t>
+          <t>3701; 11959</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP12B$herida-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$herida-Estudios-trans_dic.xlsx
@@ -530,14 +530,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -625,32 +625,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>27,29%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>11,16%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>29,58%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>18,67%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>27,29%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>11,16%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>29,58%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>0,0; 66,41</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 45,64</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 100,0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 56,88</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 66,6</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 43,86</t>
-        </is>
-      </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 100,0</t>
+          <t>0,0; 49,21</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 45,0</t>
+          <t>0,0; 40,07</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,24</t>
+          <t>0,0; 19,13</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6,07; 49,67</t>
+          <t>6,36; 51,7</t>
         </is>
       </c>
     </row>
@@ -735,32 +735,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>2,19%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2,7%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>5,28%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>2,62%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>1,99%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>4,88%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>2,19%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>2,7%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>5,28%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,04</t>
+          <t>0,0; 9,52</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,05</t>
+          <t>0,0; 8,95</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,28</t>
+          <t>1,6; 14,19</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,09</t>
+          <t>0,0; 13,6</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,56</t>
+          <t>0,0; 10,08</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,57; 14,2</t>
+          <t>0,0; 18,15</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,33</t>
+          <t>0,0; 9,47</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,75; 6,23</t>
+          <t>0,74; 6,45</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,69; 11,81</t>
+          <t>1,68; 11,1</t>
         </is>
       </c>
     </row>
@@ -845,32 +845,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>16,63%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>12,7%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>7,13%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>4,05%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>3,62%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>16,63%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>12,7%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,55</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,55</t>
+          <t>0,0; 49,23</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,69</t>
+          <t>0,0; 41,86</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 29,74</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 44,14</t>
+          <t>0,0; 20,66</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,21</t>
+          <t>0,0; 19,17</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,89</t>
+          <t>0,0; 16,58</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,43; 24,48</t>
+          <t>2,43; 23,09</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,04; 18,07</t>
+          <t>2,08; 16,98</t>
         </is>
       </c>
     </row>
@@ -955,32 +955,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>4,68%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>6,1%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>7,85%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>3,17%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>2,21%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>6,15%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>4,68%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>6,1%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>7,85%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,69</t>
+          <t>1,44; 12,2</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,75</t>
+          <t>2,18; 14,3</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,18; 13,53</t>
+          <t>2,7; 15,71</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,47; 11,77</t>
+          <t>0,0; 10,1</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,96; 13,73</t>
+          <t>0,0; 7,51</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,68; 14,96</t>
+          <t>2,05; 13,28</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,44; 8,58</t>
+          <t>1,52; 8,81</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,75; 7,98</t>
+          <t>1,94; 8,49</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,59; 11,61</t>
+          <t>3,68; 12,0</t>
         </is>
       </c>
     </row>
@@ -1105,14 +1105,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1200,32 +1200,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -1253,32 +1253,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>1502</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>787</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>662</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>1228</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>1502</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>787</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>662</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1306,47 +1306,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>0; 3655</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3217</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2239</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>0; 3743</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>0; 3665</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>0; 3091</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 2239</t>
+          <t>0; 3238</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 5020</t>
+          <t>0; 4470</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 3977</t>
+          <t>0; 3273</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>535; 4381</t>
+          <t>561; 4560</t>
         </is>
       </c>
     </row>
@@ -1368,27 +1368,27 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1416,32 +1416,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>685</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1223</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1921</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>777</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>697</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>1554</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>685</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>1223</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>1921</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 3863</t>
+          <t>0; 2984</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 3521</t>
+          <t>0; 4055</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 6135</t>
+          <t>584; 5162</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 3475</t>
+          <t>0; 4028</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 3878</t>
+          <t>0; 3531</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>570; 5166</t>
+          <t>0; 5775</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 5079</t>
+          <t>0; 5775</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>602; 5001</t>
+          <t>595; 5182</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1152; 8056</t>
+          <t>1144; 7569</t>
         </is>
       </c>
     </row>
@@ -1526,32 +1526,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1579,32 +1579,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>1865</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>1175</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>613</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>656</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>605</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>1865</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>1175</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1632,47 +1632,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 2799</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 3163</t>
+          <t>0; 5523</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 2959</t>
+          <t>0; 3871</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2557</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 4951</t>
+          <t>0; 3343</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 3533</t>
+          <t>0; 3206</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 2747</t>
+          <t>0; 3059</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>666; 6707</t>
+          <t>667; 6327</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>531; 4694</t>
+          <t>541; 4411</t>
         </is>
       </c>
     </row>
@@ -1689,32 +1689,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1742,32 +1742,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>2187</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>3875</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>3759</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>1389</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>1353</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>3388</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>2187</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>3875</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>3759</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 4251</t>
+          <t>674; 5700</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 4139</t>
+          <t>1385; 9087</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1200; 7458</t>
+          <t>1293; 7517</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>686; 5499</t>
+          <t>0; 4432</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1248; 8726</t>
+          <t>0; 4605</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1284; 7162</t>
+          <t>1129; 7318</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1306; 7770</t>
+          <t>1378; 7981</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2181; 9965</t>
+          <t>2418; 10596</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3701; 11959</t>
+          <t>3787; 12362</t>
         </is>
       </c>
     </row>
